--- a/public/data/itinerary.xlsx
+++ b/public/data/itinerary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\honeymoon\japan-trip-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B7B40B-3F8B-4C3B-A83F-68DC7BD31AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881CBB2D-6464-4E69-8B92-48820F689DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26850" yWindow="1620" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="לוז" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="90">
   <si>
     <t>תאריך (YYYY-MM-DD)</t>
   </si>
@@ -85,6 +85,12 @@
     <t>מלונות</t>
   </si>
   <si>
+    <t>מלון דוגמה — 3 לילות</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
     <t>JPY</t>
   </si>
   <si>
@@ -238,36 +244,42 @@
     <t>תחבורה מקומית</t>
   </si>
   <si>
+    <t>17:05</t>
+  </si>
+  <si>
     <t>נחיתה בשדה התעופה נריטה</t>
   </si>
   <si>
     <t>narita airport</t>
   </si>
   <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>sushiro</t>
+  </si>
+  <si>
+    <t>יפן, 〒100-0006 Tokyo, Chiyoda City, Yurakucho, 1 Chome−11−1 ビックカメラ有楽町店内 6階</t>
+  </si>
+  <si>
     <t>2026-09-06</t>
   </si>
   <si>
-    <t>sushiro</t>
+    <t>07:00</t>
   </si>
   <si>
     <t>shibuya</t>
   </si>
   <si>
+    <t>10:45</t>
+  </si>
+  <si>
     <t>בית קפה קפיברה</t>
   </si>
   <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>יפן, 〒100-0006 Tokyo, Chiyoda City, Yurakucho, 1 Chome−11−1 ビックカメラ有楽町店内 6階</t>
-  </si>
-  <si>
     <t>1 Chome-31-3 Higashimukojima, Sumida City, Tokyo 131-0032, יפן</t>
   </si>
   <si>
@@ -277,29 +289,23 @@
     <t>17:30</t>
   </si>
   <si>
+    <t>12:00</t>
+  </si>
+  <si>
     <t>נהיגה במכוניות מירוץ ברחבי טוקיו</t>
   </si>
   <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>מלון גינזה- 4 לילות</t>
-  </si>
-  <si>
-    <t>גלולות</t>
+    <t>רישיון נהיגה</t>
+  </si>
+  <si>
+    <t>רישיון נהיגה בינלאומי</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,12 +339,6 @@
       <sz val="11"/>
       <color rgb="FF1F3A5F"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -776,8 +776,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J401"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J400"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
@@ -789,7 +789,7 @@
     <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,7 +821,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -829,25 +829,25 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -858,34 +858,34 @@
         <v>75</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="2"/>
@@ -893,46 +893,46 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>12</v>
@@ -943,7 +943,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
@@ -955,7 +955,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
@@ -967,7 +967,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
@@ -979,7 +979,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="2"/>
@@ -991,7 +991,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
@@ -1003,7 +1003,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="2"/>
@@ -1015,7 +1015,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
@@ -1027,7 +1027,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="2"/>
@@ -1039,7 +1039,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="2"/>
@@ -1051,7 +1051,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="2"/>
@@ -1063,7 +1063,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="2"/>
@@ -1075,7 +1075,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="2"/>
@@ -1087,7 +1087,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="2"/>
@@ -1099,7 +1099,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="2"/>
@@ -1111,7 +1111,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="2"/>
@@ -1123,7 +1123,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="2"/>
@@ -1135,7 +1135,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="2"/>
@@ -1147,7 +1147,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="2"/>
@@ -1159,7 +1159,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="2"/>
@@ -1171,7 +1171,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="2"/>
@@ -1183,7 +1183,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
@@ -1195,7 +1195,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="2"/>
@@ -1207,7 +1207,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="2"/>
@@ -1219,7 +1219,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="2"/>
@@ -1231,7 +1231,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="2"/>
@@ -1243,7 +1243,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="2"/>
@@ -1255,7 +1255,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="2"/>
@@ -1267,7 +1267,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="2"/>
@@ -1279,7 +1279,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="2"/>
@@ -1291,7 +1291,7 @@
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="2"/>
@@ -1303,7 +1303,7 @@
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="2"/>
@@ -1315,7 +1315,7 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="2"/>
@@ -1327,7 +1327,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="2"/>
@@ -1339,7 +1339,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="2"/>
@@ -1351,7 +1351,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="2"/>
@@ -1363,7 +1363,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="2"/>
@@ -1375,7 +1375,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="2"/>
@@ -1387,7 +1387,7 @@
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="2"/>
@@ -1399,7 +1399,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="2"/>
@@ -1411,7 +1411,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="2"/>
@@ -1423,7 +1423,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="2"/>
@@ -1435,7 +1435,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
@@ -1447,7 +1447,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="2"/>
@@ -1459,7 +1459,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="2"/>
@@ -1471,7 +1471,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="2"/>
@@ -1483,7 +1483,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="2"/>
@@ -1495,7 +1495,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="2"/>
@@ -1507,7 +1507,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="2"/>
@@ -1519,7 +1519,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="2"/>
@@ -1531,7 +1531,7 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="2"/>
@@ -1543,7 +1543,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="2"/>
@@ -1555,7 +1555,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="2"/>
@@ -1567,7 +1567,7 @@
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="2"/>
@@ -1579,7 +1579,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="2"/>
@@ -1591,7 +1591,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="2"/>
@@ -1603,7 +1603,7 @@
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="2"/>
@@ -1615,7 +1615,7 @@
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="2"/>
@@ -1627,7 +1627,7 @@
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="2"/>
@@ -1639,7 +1639,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="2"/>
@@ -1651,7 +1651,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="2"/>
@@ -1663,7 +1663,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="2"/>
@@ -1675,7 +1675,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="2"/>
@@ -1687,7 +1687,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="2"/>
@@ -1699,7 +1699,7 @@
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="2"/>
@@ -1711,7 +1711,7 @@
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="2"/>
@@ -1723,7 +1723,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="2"/>
@@ -1735,7 +1735,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="2"/>
@@ -1747,7 +1747,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="2"/>
@@ -1759,7 +1759,7 @@
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="2"/>
@@ -1771,7 +1771,7 @@
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="2"/>
@@ -1783,7 +1783,7 @@
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="2"/>
@@ -1795,7 +1795,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="2"/>
@@ -1807,7 +1807,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="2"/>
@@ -1819,7 +1819,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="2"/>
@@ -1831,7 +1831,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="2"/>
@@ -1843,7 +1843,7 @@
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="2"/>
@@ -1855,7 +1855,7 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="2"/>
@@ -1867,7 +1867,7 @@
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="2"/>
@@ -1879,7 +1879,7 @@
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="2"/>
@@ -1891,7 +1891,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="2"/>
@@ -1903,7 +1903,7 @@
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="2"/>
@@ -1915,7 +1915,7 @@
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="2"/>
@@ -1927,7 +1927,7 @@
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="2"/>
@@ -1939,7 +1939,7 @@
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="2"/>
@@ -1951,7 +1951,7 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="2"/>
@@ -1963,7 +1963,7 @@
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="2"/>
@@ -1975,7 +1975,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="2"/>
@@ -1987,7 +1987,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="2"/>
@@ -1999,7 +1999,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="2"/>
@@ -2011,7 +2011,7 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="2"/>
@@ -2023,7 +2023,7 @@
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="2"/>
@@ -2035,7 +2035,7 @@
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="2"/>
@@ -2047,7 +2047,7 @@
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="2"/>
@@ -2059,7 +2059,7 @@
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="2"/>
@@ -2071,7 +2071,7 @@
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="2"/>
@@ -2083,7 +2083,7 @@
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="2"/>
@@ -2095,7 +2095,7 @@
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="2"/>
@@ -2107,7 +2107,7 @@
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="2"/>
@@ -2119,7 +2119,7 @@
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="2"/>
@@ -2131,7 +2131,7 @@
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="2"/>
@@ -2143,7 +2143,7 @@
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="2"/>
@@ -2155,7 +2155,7 @@
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="2"/>
@@ -2167,7 +2167,7 @@
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="2"/>
@@ -2179,7 +2179,7 @@
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="2"/>
@@ -2191,7 +2191,7 @@
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="2"/>
@@ -2203,7 +2203,7 @@
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="2"/>
@@ -2215,7 +2215,7 @@
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="2"/>
@@ -2227,7 +2227,7 @@
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="2"/>
@@ -2239,7 +2239,7 @@
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="2"/>
@@ -2251,7 +2251,7 @@
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="2"/>
@@ -2263,7 +2263,7 @@
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="2"/>
@@ -2275,7 +2275,7 @@
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="2"/>
@@ -2287,7 +2287,7 @@
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="2"/>
@@ -2299,7 +2299,7 @@
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="2"/>
@@ -2311,7 +2311,7 @@
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="2"/>
@@ -2323,7 +2323,7 @@
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="2"/>
@@ -2335,7 +2335,7 @@
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="2"/>
@@ -2347,7 +2347,7 @@
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="2"/>
@@ -2359,7 +2359,7 @@
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="2"/>
@@ -2371,7 +2371,7 @@
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="2"/>
@@ -2383,7 +2383,7 @@
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="2"/>
@@ -2395,7 +2395,7 @@
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="2"/>
@@ -2407,7 +2407,7 @@
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="2"/>
@@ -2419,7 +2419,7 @@
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="2"/>
@@ -2431,7 +2431,7 @@
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="2"/>
@@ -2443,7 +2443,7 @@
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="2"/>
@@ -2455,7 +2455,7 @@
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="2"/>
@@ -2467,7 +2467,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="2"/>
@@ -2479,7 +2479,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="2"/>
@@ -2491,7 +2491,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="2"/>
@@ -2503,7 +2503,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="2"/>
@@ -2515,7 +2515,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="2"/>
@@ -2527,7 +2527,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="2"/>
@@ -2539,7 +2539,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="2"/>
@@ -2551,7 +2551,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="2"/>
@@ -2563,7 +2563,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="2"/>
@@ -2575,7 +2575,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="2"/>
@@ -2587,7 +2587,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="2"/>
@@ -2599,7 +2599,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="2"/>
@@ -2611,7 +2611,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="2"/>
@@ -2623,7 +2623,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="2"/>
@@ -2635,7 +2635,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="2"/>
@@ -2647,7 +2647,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="2"/>
@@ -2659,7 +2659,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="2"/>
@@ -2671,7 +2671,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="2"/>
@@ -2683,7 +2683,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="2"/>
@@ -2695,7 +2695,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="C153" s="2"/>
@@ -2707,7 +2707,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="C154" s="2"/>
@@ -2719,7 +2719,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="C155" s="2"/>
@@ -2731,7 +2731,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="2"/>
@@ -2743,7 +2743,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="C157" s="2"/>
@@ -2755,7 +2755,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="C158" s="2"/>
@@ -2767,7 +2767,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="C159" s="2"/>
@@ -2779,7 +2779,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="C160" s="2"/>
@@ -2791,7 +2791,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="C161" s="2"/>
@@ -2803,7 +2803,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="C162" s="2"/>
@@ -2815,7 +2815,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="C163" s="2"/>
@@ -2827,7 +2827,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="C164" s="2"/>
@@ -2839,7 +2839,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="C165" s="2"/>
@@ -2851,7 +2851,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="C166" s="2"/>
@@ -2863,7 +2863,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="2"/>
@@ -2875,7 +2875,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="C168" s="2"/>
@@ -2887,7 +2887,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="C169" s="2"/>
@@ -2899,7 +2899,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="C170" s="2"/>
@@ -2911,7 +2911,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="C171" s="2"/>
@@ -2923,7 +2923,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="C172" s="2"/>
@@ -2935,7 +2935,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="C173" s="2"/>
@@ -2947,7 +2947,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="C174" s="2"/>
@@ -2959,7 +2959,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="C175" s="2"/>
@@ -2971,7 +2971,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="2"/>
@@ -2983,7 +2983,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="C177" s="2"/>
@@ -2995,7 +2995,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="C178" s="2"/>
@@ -3007,7 +3007,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="C179" s="2"/>
@@ -3019,7 +3019,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="C180" s="2"/>
@@ -3031,7 +3031,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="C181" s="2"/>
@@ -3043,7 +3043,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="C182" s="2"/>
@@ -3055,7 +3055,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="C183" s="2"/>
@@ -3067,7 +3067,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="C184" s="2"/>
@@ -3079,7 +3079,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="C185" s="2"/>
@@ -3091,7 +3091,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="2"/>
@@ -3103,7 +3103,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="C187" s="2"/>
@@ -3115,7 +3115,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="2"/>
@@ -3127,7 +3127,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="C189" s="2"/>
@@ -3139,7 +3139,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="C190" s="2"/>
@@ -3151,7 +3151,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="C191" s="2"/>
@@ -3163,7 +3163,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="C192" s="2"/>
@@ -3175,7 +3175,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="C193" s="2"/>
@@ -3187,7 +3187,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="C194" s="2"/>
@@ -3199,7 +3199,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="C195" s="2"/>
@@ -3211,7 +3211,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="2"/>
@@ -3223,7 +3223,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="2"/>
@@ -3235,7 +3235,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="3"/>
       <c r="C198" s="2"/>
@@ -3247,7 +3247,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="3"/>
       <c r="C199" s="2"/>
@@ -3259,7 +3259,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="3"/>
       <c r="C200" s="2"/>
@@ -3271,7 +3271,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="3"/>
       <c r="C201" s="2"/>
@@ -3283,7 +3283,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="3"/>
       <c r="C202" s="2"/>
@@ -3295,7 +3295,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" s="2"/>
       <c r="B203" s="3"/>
       <c r="C203" s="2"/>
@@ -3307,7 +3307,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" s="2"/>
       <c r="B204" s="3"/>
       <c r="C204" s="2"/>
@@ -3319,7 +3319,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205" s="2"/>
       <c r="B205" s="3"/>
       <c r="C205" s="2"/>
@@ -3331,7 +3331,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206" s="2"/>
       <c r="B206" s="3"/>
       <c r="C206" s="2"/>
@@ -3343,7 +3343,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207" s="2"/>
       <c r="B207" s="3"/>
       <c r="C207" s="2"/>
@@ -3355,7 +3355,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208" s="2"/>
       <c r="B208" s="3"/>
       <c r="C208" s="2"/>
@@ -3367,7 +3367,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209" s="2"/>
       <c r="B209" s="3"/>
       <c r="C209" s="2"/>
@@ -3379,7 +3379,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A210" s="2"/>
       <c r="B210" s="3"/>
       <c r="C210" s="2"/>
@@ -3391,7 +3391,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A211" s="2"/>
       <c r="B211" s="3"/>
       <c r="C211" s="2"/>
@@ -3403,7 +3403,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A212" s="2"/>
       <c r="B212" s="3"/>
       <c r="C212" s="2"/>
@@ -3415,7 +3415,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="3"/>
       <c r="C213" s="2"/>
@@ -3427,7 +3427,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A214" s="2"/>
       <c r="B214" s="3"/>
       <c r="C214" s="2"/>
@@ -3439,7 +3439,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A215" s="2"/>
       <c r="B215" s="3"/>
       <c r="C215" s="2"/>
@@ -3451,7 +3451,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A216" s="2"/>
       <c r="B216" s="3"/>
       <c r="C216" s="2"/>
@@ -3463,7 +3463,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A217" s="2"/>
       <c r="B217" s="3"/>
       <c r="C217" s="2"/>
@@ -3475,7 +3475,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A218" s="2"/>
       <c r="B218" s="3"/>
       <c r="C218" s="2"/>
@@ -3487,7 +3487,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A219" s="2"/>
       <c r="B219" s="3"/>
       <c r="C219" s="2"/>
@@ -3499,7 +3499,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A220" s="2"/>
       <c r="B220" s="3"/>
       <c r="C220" s="2"/>
@@ -3511,7 +3511,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A221" s="2"/>
       <c r="B221" s="3"/>
       <c r="C221" s="2"/>
@@ -3523,7 +3523,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A222" s="2"/>
       <c r="B222" s="3"/>
       <c r="C222" s="2"/>
@@ -3535,7 +3535,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A223" s="2"/>
       <c r="B223" s="3"/>
       <c r="C223" s="2"/>
@@ -3547,7 +3547,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A224" s="2"/>
       <c r="B224" s="3"/>
       <c r="C224" s="2"/>
@@ -3559,7 +3559,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A225" s="2"/>
       <c r="B225" s="3"/>
       <c r="C225" s="2"/>
@@ -3571,7 +3571,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A226" s="2"/>
       <c r="B226" s="3"/>
       <c r="C226" s="2"/>
@@ -3583,7 +3583,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A227" s="2"/>
       <c r="B227" s="3"/>
       <c r="C227" s="2"/>
@@ -3595,7 +3595,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="3"/>
       <c r="C228" s="2"/>
@@ -3607,7 +3607,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
       <c r="B229" s="3"/>
       <c r="C229" s="2"/>
@@ -3619,7 +3619,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A230" s="2"/>
       <c r="B230" s="3"/>
       <c r="C230" s="2"/>
@@ -3631,7 +3631,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A231" s="2"/>
       <c r="B231" s="3"/>
       <c r="C231" s="2"/>
@@ -3643,7 +3643,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A232" s="2"/>
       <c r="B232" s="3"/>
       <c r="C232" s="2"/>
@@ -3655,7 +3655,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A233" s="2"/>
       <c r="B233" s="3"/>
       <c r="C233" s="2"/>
@@ -3667,7 +3667,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A234" s="2"/>
       <c r="B234" s="3"/>
       <c r="C234" s="2"/>
@@ -3679,7 +3679,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A235" s="2"/>
       <c r="B235" s="3"/>
       <c r="C235" s="2"/>
@@ -3691,7 +3691,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A236" s="2"/>
       <c r="B236" s="3"/>
       <c r="C236" s="2"/>
@@ -3703,7 +3703,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A237" s="2"/>
       <c r="B237" s="3"/>
       <c r="C237" s="2"/>
@@ -3715,7 +3715,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A238" s="2"/>
       <c r="B238" s="3"/>
       <c r="C238" s="2"/>
@@ -3727,7 +3727,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A239" s="2"/>
       <c r="B239" s="3"/>
       <c r="C239" s="2"/>
@@ -3739,7 +3739,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A240" s="2"/>
       <c r="B240" s="3"/>
       <c r="C240" s="2"/>
@@ -3751,7 +3751,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A241" s="2"/>
       <c r="B241" s="3"/>
       <c r="C241" s="2"/>
@@ -3763,7 +3763,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A242" s="2"/>
       <c r="B242" s="3"/>
       <c r="C242" s="2"/>
@@ -3775,7 +3775,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="3"/>
       <c r="C243" s="2"/>
@@ -3787,7 +3787,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A244" s="2"/>
       <c r="B244" s="3"/>
       <c r="C244" s="2"/>
@@ -3799,7 +3799,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A245" s="2"/>
       <c r="B245" s="3"/>
       <c r="C245" s="2"/>
@@ -3811,7 +3811,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A246" s="2"/>
       <c r="B246" s="3"/>
       <c r="C246" s="2"/>
@@ -3823,7 +3823,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A247" s="2"/>
       <c r="B247" s="3"/>
       <c r="C247" s="2"/>
@@ -3835,7 +3835,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A248" s="2"/>
       <c r="B248" s="3"/>
       <c r="C248" s="2"/>
@@ -3847,7 +3847,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A249" s="2"/>
       <c r="B249" s="3"/>
       <c r="C249" s="2"/>
@@ -3859,7 +3859,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A250" s="2"/>
       <c r="B250" s="3"/>
       <c r="C250" s="2"/>
@@ -3871,7 +3871,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A251" s="2"/>
       <c r="B251" s="3"/>
       <c r="C251" s="2"/>
@@ -3883,7 +3883,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A252" s="2"/>
       <c r="B252" s="3"/>
       <c r="C252" s="2"/>
@@ -3895,7 +3895,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A253" s="2"/>
       <c r="B253" s="3"/>
       <c r="C253" s="2"/>
@@ -3907,7 +3907,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A254" s="2"/>
       <c r="B254" s="3"/>
       <c r="C254" s="2"/>
@@ -3919,7 +3919,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A255" s="2"/>
       <c r="B255" s="3"/>
       <c r="C255" s="2"/>
@@ -3931,7 +3931,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A256" s="2"/>
       <c r="B256" s="3"/>
       <c r="C256" s="2"/>
@@ -3943,7 +3943,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A257" s="2"/>
       <c r="B257" s="3"/>
       <c r="C257" s="2"/>
@@ -3955,7 +3955,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A258" s="2"/>
       <c r="B258" s="3"/>
       <c r="C258" s="2"/>
@@ -3967,7 +3967,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A259" s="2"/>
       <c r="B259" s="3"/>
       <c r="C259" s="2"/>
@@ -3979,7 +3979,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A260" s="2"/>
       <c r="B260" s="3"/>
       <c r="C260" s="2"/>
@@ -3991,7 +3991,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A261" s="2"/>
       <c r="B261" s="3"/>
       <c r="C261" s="2"/>
@@ -4003,7 +4003,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A262" s="2"/>
       <c r="B262" s="3"/>
       <c r="C262" s="2"/>
@@ -4015,7 +4015,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A263" s="2"/>
       <c r="B263" s="3"/>
       <c r="C263" s="2"/>
@@ -4027,7 +4027,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A264" s="2"/>
       <c r="B264" s="3"/>
       <c r="C264" s="2"/>
@@ -4039,7 +4039,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A265" s="2"/>
       <c r="B265" s="3"/>
       <c r="C265" s="2"/>
@@ -4051,7 +4051,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A266" s="2"/>
       <c r="B266" s="3"/>
       <c r="C266" s="2"/>
@@ -4063,7 +4063,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A267" s="2"/>
       <c r="B267" s="3"/>
       <c r="C267" s="2"/>
@@ -4075,7 +4075,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A268" s="2"/>
       <c r="B268" s="3"/>
       <c r="C268" s="2"/>
@@ -4087,7 +4087,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A269" s="2"/>
       <c r="B269" s="3"/>
       <c r="C269" s="2"/>
@@ -4099,7 +4099,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A270" s="2"/>
       <c r="B270" s="3"/>
       <c r="C270" s="2"/>
@@ -4111,7 +4111,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A271" s="2"/>
       <c r="B271" s="3"/>
       <c r="C271" s="2"/>
@@ -4123,7 +4123,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A272" s="2"/>
       <c r="B272" s="3"/>
       <c r="C272" s="2"/>
@@ -4135,7 +4135,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A273" s="2"/>
       <c r="B273" s="3"/>
       <c r="C273" s="2"/>
@@ -4147,7 +4147,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A274" s="2"/>
       <c r="B274" s="3"/>
       <c r="C274" s="2"/>
@@ -4159,7 +4159,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A275" s="2"/>
       <c r="B275" s="3"/>
       <c r="C275" s="2"/>
@@ -4171,7 +4171,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A276" s="2"/>
       <c r="B276" s="3"/>
       <c r="C276" s="2"/>
@@ -4183,7 +4183,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A277" s="2"/>
       <c r="B277" s="3"/>
       <c r="C277" s="2"/>
@@ -4195,7 +4195,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A278" s="2"/>
       <c r="B278" s="3"/>
       <c r="C278" s="2"/>
@@ -4207,7 +4207,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A279" s="2"/>
       <c r="B279" s="3"/>
       <c r="C279" s="2"/>
@@ -4219,7 +4219,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A280" s="2"/>
       <c r="B280" s="3"/>
       <c r="C280" s="2"/>
@@ -4231,7 +4231,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A281" s="2"/>
       <c r="B281" s="3"/>
       <c r="C281" s="2"/>
@@ -4243,7 +4243,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A282" s="2"/>
       <c r="B282" s="3"/>
       <c r="C282" s="2"/>
@@ -4255,7 +4255,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A283" s="2"/>
       <c r="B283" s="3"/>
       <c r="C283" s="2"/>
@@ -4267,7 +4267,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A284" s="2"/>
       <c r="B284" s="3"/>
       <c r="C284" s="2"/>
@@ -4279,7 +4279,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A285" s="2"/>
       <c r="B285" s="3"/>
       <c r="C285" s="2"/>
@@ -4291,7 +4291,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A286" s="2"/>
       <c r="B286" s="3"/>
       <c r="C286" s="2"/>
@@ -4303,7 +4303,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A287" s="2"/>
       <c r="B287" s="3"/>
       <c r="C287" s="2"/>
@@ -4315,7 +4315,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A288" s="2"/>
       <c r="B288" s="3"/>
       <c r="C288" s="2"/>
@@ -4327,7 +4327,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A289" s="2"/>
       <c r="B289" s="3"/>
       <c r="C289" s="2"/>
@@ -4339,7 +4339,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A290" s="2"/>
       <c r="B290" s="3"/>
       <c r="C290" s="2"/>
@@ -4351,7 +4351,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A291" s="2"/>
       <c r="B291" s="3"/>
       <c r="C291" s="2"/>
@@ -4363,7 +4363,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A292" s="2"/>
       <c r="B292" s="3"/>
       <c r="C292" s="2"/>
@@ -4375,7 +4375,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A293" s="2"/>
       <c r="B293" s="3"/>
       <c r="C293" s="2"/>
@@ -4387,7 +4387,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A294" s="2"/>
       <c r="B294" s="3"/>
       <c r="C294" s="2"/>
@@ -4399,7 +4399,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A295" s="2"/>
       <c r="B295" s="3"/>
       <c r="C295" s="2"/>
@@ -4411,7 +4411,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A296" s="2"/>
       <c r="B296" s="3"/>
       <c r="C296" s="2"/>
@@ -4423,7 +4423,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A297" s="2"/>
       <c r="B297" s="3"/>
       <c r="C297" s="2"/>
@@ -4435,7 +4435,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A298" s="2"/>
       <c r="B298" s="3"/>
       <c r="C298" s="2"/>
@@ -4447,7 +4447,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A299" s="2"/>
       <c r="B299" s="3"/>
       <c r="C299" s="2"/>
@@ -4459,7 +4459,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A300" s="2"/>
       <c r="B300" s="3"/>
       <c r="C300" s="2"/>
@@ -4471,7 +4471,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A301" s="2"/>
       <c r="B301" s="3"/>
       <c r="C301" s="2"/>
@@ -4483,7 +4483,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A302" s="2"/>
       <c r="B302" s="3"/>
       <c r="C302" s="2"/>
@@ -4495,7 +4495,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A303" s="2"/>
       <c r="B303" s="3"/>
       <c r="C303" s="2"/>
@@ -4507,7 +4507,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A304" s="2"/>
       <c r="B304" s="3"/>
       <c r="C304" s="2"/>
@@ -4519,7 +4519,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A305" s="2"/>
       <c r="B305" s="3"/>
       <c r="C305" s="2"/>
@@ -4531,7 +4531,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A306" s="2"/>
       <c r="B306" s="3"/>
       <c r="C306" s="2"/>
@@ -4543,7 +4543,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A307" s="2"/>
       <c r="B307" s="3"/>
       <c r="C307" s="2"/>
@@ -4555,7 +4555,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A308" s="2"/>
       <c r="B308" s="3"/>
       <c r="C308" s="2"/>
@@ -4567,7 +4567,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A309" s="2"/>
       <c r="B309" s="3"/>
       <c r="C309" s="2"/>
@@ -4579,7 +4579,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A310" s="2"/>
       <c r="B310" s="3"/>
       <c r="C310" s="2"/>
@@ -4591,7 +4591,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A311" s="2"/>
       <c r="B311" s="3"/>
       <c r="C311" s="2"/>
@@ -4603,7 +4603,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A312" s="2"/>
       <c r="B312" s="3"/>
       <c r="C312" s="2"/>
@@ -4615,7 +4615,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A313" s="2"/>
       <c r="B313" s="3"/>
       <c r="C313" s="2"/>
@@ -4627,7 +4627,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A314" s="2"/>
       <c r="B314" s="3"/>
       <c r="C314" s="2"/>
@@ -4639,7 +4639,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A315" s="2"/>
       <c r="B315" s="3"/>
       <c r="C315" s="2"/>
@@ -4651,7 +4651,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A316" s="2"/>
       <c r="B316" s="3"/>
       <c r="C316" s="2"/>
@@ -4663,7 +4663,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A317" s="2"/>
       <c r="B317" s="3"/>
       <c r="C317" s="2"/>
@@ -4675,7 +4675,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A318" s="2"/>
       <c r="B318" s="3"/>
       <c r="C318" s="2"/>
@@ -4687,7 +4687,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A319" s="2"/>
       <c r="B319" s="3"/>
       <c r="C319" s="2"/>
@@ -4699,7 +4699,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A320" s="2"/>
       <c r="B320" s="3"/>
       <c r="C320" s="2"/>
@@ -4711,7 +4711,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A321" s="2"/>
       <c r="B321" s="3"/>
       <c r="C321" s="2"/>
@@ -4723,7 +4723,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A322" s="2"/>
       <c r="B322" s="3"/>
       <c r="C322" s="2"/>
@@ -4735,7 +4735,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A323" s="2"/>
       <c r="B323" s="3"/>
       <c r="C323" s="2"/>
@@ -4747,7 +4747,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A324" s="2"/>
       <c r="B324" s="3"/>
       <c r="C324" s="2"/>
@@ -4759,7 +4759,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A325" s="2"/>
       <c r="B325" s="3"/>
       <c r="C325" s="2"/>
@@ -4771,7 +4771,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A326" s="2"/>
       <c r="B326" s="3"/>
       <c r="C326" s="2"/>
@@ -4783,7 +4783,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A327" s="2"/>
       <c r="B327" s="3"/>
       <c r="C327" s="2"/>
@@ -4795,7 +4795,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A328" s="2"/>
       <c r="B328" s="3"/>
       <c r="C328" s="2"/>
@@ -4807,7 +4807,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A329" s="2"/>
       <c r="B329" s="3"/>
       <c r="C329" s="2"/>
@@ -4819,7 +4819,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A330" s="2"/>
       <c r="B330" s="3"/>
       <c r="C330" s="2"/>
@@ -4831,7 +4831,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A331" s="2"/>
       <c r="B331" s="3"/>
       <c r="C331" s="2"/>
@@ -4843,7 +4843,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A332" s="2"/>
       <c r="B332" s="3"/>
       <c r="C332" s="2"/>
@@ -4855,7 +4855,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A333" s="2"/>
       <c r="B333" s="3"/>
       <c r="C333" s="2"/>
@@ -4867,7 +4867,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A334" s="2"/>
       <c r="B334" s="3"/>
       <c r="C334" s="2"/>
@@ -4879,7 +4879,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A335" s="2"/>
       <c r="B335" s="3"/>
       <c r="C335" s="2"/>
@@ -4891,7 +4891,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A336" s="2"/>
       <c r="B336" s="3"/>
       <c r="C336" s="2"/>
@@ -4903,7 +4903,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A337" s="2"/>
       <c r="B337" s="3"/>
       <c r="C337" s="2"/>
@@ -4915,7 +4915,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A338" s="2"/>
       <c r="B338" s="3"/>
       <c r="C338" s="2"/>
@@ -4927,7 +4927,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A339" s="2"/>
       <c r="B339" s="3"/>
       <c r="C339" s="2"/>
@@ -4939,7 +4939,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A340" s="2"/>
       <c r="B340" s="3"/>
       <c r="C340" s="2"/>
@@ -4951,7 +4951,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A341" s="2"/>
       <c r="B341" s="3"/>
       <c r="C341" s="2"/>
@@ -4963,7 +4963,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A342" s="2"/>
       <c r="B342" s="3"/>
       <c r="C342" s="2"/>
@@ -4975,7 +4975,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A343" s="2"/>
       <c r="B343" s="3"/>
       <c r="C343" s="2"/>
@@ -4987,7 +4987,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A344" s="2"/>
       <c r="B344" s="3"/>
       <c r="C344" s="2"/>
@@ -4999,7 +4999,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A345" s="2"/>
       <c r="B345" s="3"/>
       <c r="C345" s="2"/>
@@ -5011,7 +5011,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A346" s="2"/>
       <c r="B346" s="3"/>
       <c r="C346" s="2"/>
@@ -5023,7 +5023,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A347" s="2"/>
       <c r="B347" s="3"/>
       <c r="C347" s="2"/>
@@ -5035,7 +5035,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A348" s="2"/>
       <c r="B348" s="3"/>
       <c r="C348" s="2"/>
@@ -5047,7 +5047,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A349" s="2"/>
       <c r="B349" s="3"/>
       <c r="C349" s="2"/>
@@ -5059,7 +5059,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A350" s="2"/>
       <c r="B350" s="3"/>
       <c r="C350" s="2"/>
@@ -5071,7 +5071,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A351" s="2"/>
       <c r="B351" s="3"/>
       <c r="C351" s="2"/>
@@ -5083,7 +5083,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A352" s="2"/>
       <c r="B352" s="3"/>
       <c r="C352" s="2"/>
@@ -5095,7 +5095,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A353" s="2"/>
       <c r="B353" s="3"/>
       <c r="C353" s="2"/>
@@ -5107,7 +5107,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A354" s="2"/>
       <c r="B354" s="3"/>
       <c r="C354" s="2"/>
@@ -5119,7 +5119,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A355" s="2"/>
       <c r="B355" s="3"/>
       <c r="C355" s="2"/>
@@ -5131,7 +5131,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A356" s="2"/>
       <c r="B356" s="3"/>
       <c r="C356" s="2"/>
@@ -5143,7 +5143,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A357" s="2"/>
       <c r="B357" s="3"/>
       <c r="C357" s="2"/>
@@ -5155,7 +5155,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A358" s="2"/>
       <c r="B358" s="3"/>
       <c r="C358" s="2"/>
@@ -5167,7 +5167,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A359" s="2"/>
       <c r="B359" s="3"/>
       <c r="C359" s="2"/>
@@ -5179,7 +5179,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A360" s="2"/>
       <c r="B360" s="3"/>
       <c r="C360" s="2"/>
@@ -5191,7 +5191,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A361" s="2"/>
       <c r="B361" s="3"/>
       <c r="C361" s="2"/>
@@ -5203,7 +5203,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A362" s="2"/>
       <c r="B362" s="3"/>
       <c r="C362" s="2"/>
@@ -5215,7 +5215,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A363" s="2"/>
       <c r="B363" s="3"/>
       <c r="C363" s="2"/>
@@ -5227,7 +5227,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A364" s="2"/>
       <c r="B364" s="3"/>
       <c r="C364" s="2"/>
@@ -5239,7 +5239,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A365" s="2"/>
       <c r="B365" s="3"/>
       <c r="C365" s="2"/>
@@ -5251,7 +5251,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A366" s="2"/>
       <c r="B366" s="3"/>
       <c r="C366" s="2"/>
@@ -5263,7 +5263,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A367" s="2"/>
       <c r="B367" s="3"/>
       <c r="C367" s="2"/>
@@ -5275,7 +5275,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A368" s="2"/>
       <c r="B368" s="3"/>
       <c r="C368" s="2"/>
@@ -5287,7 +5287,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A369" s="2"/>
       <c r="B369" s="3"/>
       <c r="C369" s="2"/>
@@ -5299,7 +5299,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A370" s="2"/>
       <c r="B370" s="3"/>
       <c r="C370" s="2"/>
@@ -5311,7 +5311,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A371" s="2"/>
       <c r="B371" s="3"/>
       <c r="C371" s="2"/>
@@ -5323,7 +5323,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A372" s="2"/>
       <c r="B372" s="3"/>
       <c r="C372" s="2"/>
@@ -5335,7 +5335,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A373" s="2"/>
       <c r="B373" s="3"/>
       <c r="C373" s="2"/>
@@ -5347,7 +5347,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A374" s="2"/>
       <c r="B374" s="3"/>
       <c r="C374" s="2"/>
@@ -5359,7 +5359,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A375" s="2"/>
       <c r="B375" s="3"/>
       <c r="C375" s="2"/>
@@ -5371,7 +5371,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A376" s="2"/>
       <c r="B376" s="3"/>
       <c r="C376" s="2"/>
@@ -5383,7 +5383,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A377" s="2"/>
       <c r="B377" s="3"/>
       <c r="C377" s="2"/>
@@ -5395,7 +5395,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A378" s="2"/>
       <c r="B378" s="3"/>
       <c r="C378" s="2"/>
@@ -5407,7 +5407,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A379" s="2"/>
       <c r="B379" s="3"/>
       <c r="C379" s="2"/>
@@ -5419,7 +5419,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A380" s="2"/>
       <c r="B380" s="3"/>
       <c r="C380" s="2"/>
@@ -5431,7 +5431,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A381" s="2"/>
       <c r="B381" s="3"/>
       <c r="C381" s="2"/>
@@ -5443,7 +5443,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A382" s="2"/>
       <c r="B382" s="3"/>
       <c r="C382" s="2"/>
@@ -5455,7 +5455,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A383" s="2"/>
       <c r="B383" s="3"/>
       <c r="C383" s="2"/>
@@ -5467,7 +5467,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A384" s="2"/>
       <c r="B384" s="3"/>
       <c r="C384" s="2"/>
@@ -5479,7 +5479,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A385" s="2"/>
       <c r="B385" s="3"/>
       <c r="C385" s="2"/>
@@ -5491,7 +5491,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A386" s="2"/>
       <c r="B386" s="3"/>
       <c r="C386" s="2"/>
@@ -5503,7 +5503,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A387" s="2"/>
       <c r="B387" s="3"/>
       <c r="C387" s="2"/>
@@ -5515,7 +5515,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A388" s="2"/>
       <c r="B388" s="3"/>
       <c r="C388" s="2"/>
@@ -5527,7 +5527,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A389" s="2"/>
       <c r="B389" s="3"/>
       <c r="C389" s="2"/>
@@ -5539,7 +5539,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A390" s="2"/>
       <c r="B390" s="3"/>
       <c r="C390" s="2"/>
@@ -5551,7 +5551,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A391" s="2"/>
       <c r="B391" s="3"/>
       <c r="C391" s="2"/>
@@ -5563,7 +5563,7 @@
       <c r="I391" s="3"/>
       <c r="J391" s="3"/>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A392" s="2"/>
       <c r="B392" s="3"/>
       <c r="C392" s="2"/>
@@ -5575,7 +5575,7 @@
       <c r="I392" s="3"/>
       <c r="J392" s="3"/>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A393" s="2"/>
       <c r="B393" s="3"/>
       <c r="C393" s="2"/>
@@ -5587,7 +5587,7 @@
       <c r="I393" s="3"/>
       <c r="J393" s="3"/>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A394" s="2"/>
       <c r="B394" s="3"/>
       <c r="C394" s="2"/>
@@ -5599,7 +5599,7 @@
       <c r="I394" s="3"/>
       <c r="J394" s="3"/>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A395" s="2"/>
       <c r="B395" s="3"/>
       <c r="C395" s="2"/>
@@ -5611,7 +5611,7 @@
       <c r="I395" s="3"/>
       <c r="J395" s="3"/>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A396" s="2"/>
       <c r="B396" s="3"/>
       <c r="C396" s="2"/>
@@ -5623,7 +5623,7 @@
       <c r="I396" s="3"/>
       <c r="J396" s="3"/>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A397" s="2"/>
       <c r="B397" s="3"/>
       <c r="C397" s="2"/>
@@ -5635,7 +5635,7 @@
       <c r="I397" s="3"/>
       <c r="J397" s="3"/>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A398" s="2"/>
       <c r="B398" s="3"/>
       <c r="C398" s="2"/>
@@ -5647,7 +5647,7 @@
       <c r="I398" s="3"/>
       <c r="J398" s="3"/>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A399" s="2"/>
       <c r="B399" s="3"/>
       <c r="C399" s="2"/>
@@ -5659,7 +5659,7 @@
       <c r="I399" s="3"/>
       <c r="J399" s="3"/>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A400" s="2"/>
       <c r="B400" s="3"/>
       <c r="C400" s="2"/>
@@ -5671,21 +5671,8 @@
       <c r="I400" s="3"/>
       <c r="J400" s="3"/>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A401" s="2"/>
-      <c r="B401" s="3"/>
-      <c r="C401" s="2"/>
-      <c r="D401" s="3"/>
-      <c r="E401" s="3"/>
-      <c r="F401" s="3"/>
-      <c r="G401" s="2"/>
-      <c r="H401" s="2"/>
-      <c r="I401" s="3"/>
-      <c r="J401" s="3"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K008000 OFFICIAL&amp;1#_x000D_</oddHeader>
@@ -5698,13 +5685,13 @@
           <x14:formula1>
             <xm:f>רשימות!$A$1:$A$15</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D6 B2:B401</xm:sqref>
+          <xm:sqref>B2:B400</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>רשימות!$B$1:$B$10</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E401</xm:sqref>
+          <xm:sqref>E2:E400</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5715,7 +5702,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E200"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -5724,7 +5711,7 @@
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5741,7 +5728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -5749,1395 +5736,1395 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1573</v>
+        <v>18</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -7181,482 +7168,484 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A149"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
     </row>
   </sheetData>
@@ -7672,210 +7661,210 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="19"/>
     </row>
-    <row r="4" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B4" s="19"/>
     </row>
-    <row r="5" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" s="19"/>
     </row>
-    <row r="6" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="19"/>
     </row>
-    <row r="7" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" s="19"/>
     </row>
-    <row r="8" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="19"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
       <c r="B13" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11"/>
       <c r="B14" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14"/>
       <c r="B17" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="16"/>
       <c r="B19" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
         <v>11</v>
       </c>
       <c r="B23" s="19"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="19"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B25" s="19"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B26" s="19"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B27" s="19"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B28" s="19"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B29" s="19"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B30" s="19"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B31" s="19"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B32" s="19"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B33" s="19"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B34" s="19"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B35" s="19"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B36" s="19"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B37" s="19"/>
     </row>
@@ -7914,12 +7903,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -7927,131 +7916,131 @@
         <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/itinerary.xlsx
+++ b/public/data/itinerary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\honeymoon\japan-trip-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B7B40B-3F8B-4C3B-A83F-68DC7BD31AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7578A8E-98DD-4CD3-AD50-C30F90F3A0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="לוז" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="90">
   <si>
     <t>תאריך (YYYY-MM-DD)</t>
   </si>
@@ -85,6 +85,12 @@
     <t>מלונות</t>
   </si>
   <si>
+    <t>מלון דוגמה — 3 לילות</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
     <t>JPY</t>
   </si>
   <si>
@@ -238,36 +244,42 @@
     <t>תחבורה מקומית</t>
   </si>
   <si>
+    <t>17:05</t>
+  </si>
+  <si>
     <t>נחיתה בשדה התעופה נריטה</t>
   </si>
   <si>
     <t>narita airport</t>
   </si>
   <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>sushiro</t>
+  </si>
+  <si>
+    <t>יפן, 〒100-0006 Tokyo, Chiyoda City, Yurakucho, 1 Chome−11−1 ビックカメラ有楽町店内 6階</t>
+  </si>
+  <si>
     <t>2026-09-06</t>
   </si>
   <si>
-    <t>sushiro</t>
+    <t>07:00</t>
   </si>
   <si>
     <t>shibuya</t>
   </si>
   <si>
+    <t>10:45</t>
+  </si>
+  <si>
     <t>בית קפה קפיברה</t>
   </si>
   <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>יפן, 〒100-0006 Tokyo, Chiyoda City, Yurakucho, 1 Chome−11−1 ビックカメラ有楽町店内 6階</t>
-  </si>
-  <si>
     <t>1 Chome-31-3 Higashimukojima, Sumida City, Tokyo 131-0032, יפן</t>
   </si>
   <si>
@@ -277,29 +289,23 @@
     <t>17:30</t>
   </si>
   <si>
+    <t>12:00</t>
+  </si>
+  <si>
     <t>נהיגה במכוניות מירוץ ברחבי טוקיו</t>
   </si>
   <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>מלון גינזה- 4 לילות</t>
-  </si>
-  <si>
-    <t>גלולות</t>
+    <t>רישיון נהיגה</t>
+  </si>
+  <si>
+    <t>רישיון נהיגה בינלאומי</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,12 +339,6 @@
       <sz val="11"/>
       <color rgb="FF1F3A5F"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -776,8 +776,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J401"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J400"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
@@ -789,7 +789,7 @@
     <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,7 +821,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -829,25 +829,25 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -858,34 +858,34 @@
         <v>75</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="2"/>
@@ -893,46 +893,46 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>12</v>
@@ -943,7 +943,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
@@ -955,7 +955,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
@@ -967,7 +967,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
@@ -979,7 +979,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="2"/>
@@ -991,7 +991,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
@@ -1003,7 +1003,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="2"/>
@@ -1015,7 +1015,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
@@ -1027,7 +1027,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="2"/>
@@ -1039,7 +1039,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="2"/>
@@ -1051,7 +1051,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="2"/>
@@ -1063,7 +1063,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="2"/>
@@ -1075,7 +1075,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="2"/>
@@ -1087,7 +1087,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="2"/>
@@ -1099,7 +1099,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="2"/>
@@ -1111,7 +1111,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="2"/>
@@ -1123,7 +1123,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="2"/>
@@ -1135,7 +1135,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="2"/>
@@ -1147,7 +1147,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="2"/>
@@ -1159,7 +1159,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="2"/>
@@ -1171,7 +1171,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="2"/>
@@ -1183,7 +1183,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
@@ -1195,7 +1195,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="2"/>
@@ -1207,7 +1207,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="2"/>
@@ -1219,7 +1219,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="2"/>
@@ -1231,7 +1231,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="2"/>
@@ -1243,7 +1243,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="2"/>
@@ -1255,7 +1255,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="2"/>
@@ -1267,7 +1267,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="2"/>
@@ -1279,7 +1279,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="2"/>
@@ -1291,7 +1291,7 @@
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="2"/>
@@ -1303,7 +1303,7 @@
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="2"/>
@@ -1315,7 +1315,7 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="2"/>
@@ -1327,7 +1327,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="2"/>
@@ -1339,7 +1339,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="2"/>
@@ -1351,7 +1351,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="2"/>
@@ -1363,7 +1363,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="2"/>
@@ -1375,7 +1375,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="2"/>
@@ -1387,7 +1387,7 @@
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="2"/>
@@ -1399,7 +1399,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="2"/>
@@ -1411,7 +1411,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="2"/>
@@ -1423,7 +1423,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="2"/>
@@ -1435,7 +1435,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
@@ -1447,7 +1447,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="2"/>
@@ -1459,7 +1459,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="2"/>
@@ -1471,7 +1471,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="2"/>
@@ -1483,7 +1483,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="2"/>
@@ -1495,7 +1495,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="2"/>
@@ -1507,7 +1507,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="2"/>
@@ -1519,7 +1519,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="2"/>
@@ -1531,7 +1531,7 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="2"/>
@@ -1543,7 +1543,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="2"/>
@@ -1555,7 +1555,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="2"/>
@@ -1567,7 +1567,7 @@
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="2"/>
@@ -1579,7 +1579,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="2"/>
@@ -1591,7 +1591,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="2"/>
@@ -1603,7 +1603,7 @@
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="2"/>
@@ -1615,7 +1615,7 @@
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="2"/>
@@ -1627,7 +1627,7 @@
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="2"/>
@@ -1639,7 +1639,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="2"/>
@@ -1651,7 +1651,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="2"/>
@@ -1663,7 +1663,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="2"/>
@@ -1675,7 +1675,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="2"/>
@@ -1687,7 +1687,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="2"/>
@@ -1699,7 +1699,7 @@
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="2"/>
@@ -1711,7 +1711,7 @@
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="2"/>
@@ -1723,7 +1723,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="2"/>
@@ -1735,7 +1735,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="2"/>
@@ -1747,7 +1747,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="2"/>
@@ -1759,7 +1759,7 @@
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="2"/>
@@ -1771,7 +1771,7 @@
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="2"/>
@@ -1783,7 +1783,7 @@
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="2"/>
@@ -1795,7 +1795,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="2"/>
@@ -1807,7 +1807,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="2"/>
@@ -1819,7 +1819,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="2"/>
@@ -1831,7 +1831,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="2"/>
@@ -1843,7 +1843,7 @@
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="2"/>
@@ -1855,7 +1855,7 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="2"/>
@@ -1867,7 +1867,7 @@
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="2"/>
@@ -1879,7 +1879,7 @@
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="2"/>
@@ -1891,7 +1891,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="2"/>
@@ -1903,7 +1903,7 @@
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="2"/>
@@ -1915,7 +1915,7 @@
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="2"/>
@@ -1927,7 +1927,7 @@
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="2"/>
@@ -1939,7 +1939,7 @@
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="2"/>
@@ -1951,7 +1951,7 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="2"/>
@@ -1963,7 +1963,7 @@
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="2"/>
@@ -1975,7 +1975,7 @@
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="2"/>
@@ -1987,7 +1987,7 @@
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="2"/>
@@ -1999,7 +1999,7 @@
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="2"/>
@@ -2011,7 +2011,7 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="2"/>
@@ -2023,7 +2023,7 @@
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="2"/>
@@ -2035,7 +2035,7 @@
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="2"/>
@@ -2047,7 +2047,7 @@
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="2"/>
@@ -2059,7 +2059,7 @@
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="2"/>
@@ -2071,7 +2071,7 @@
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="2"/>
@@ -2083,7 +2083,7 @@
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="2"/>
@@ -2095,7 +2095,7 @@
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="2"/>
@@ -2107,7 +2107,7 @@
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="2"/>
@@ -2119,7 +2119,7 @@
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="2"/>
@@ -2131,7 +2131,7 @@
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="2"/>
@@ -2143,7 +2143,7 @@
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="2"/>
@@ -2155,7 +2155,7 @@
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="2"/>
@@ -2167,7 +2167,7 @@
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="2"/>
@@ -2179,7 +2179,7 @@
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="2"/>
@@ -2191,7 +2191,7 @@
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="2"/>
@@ -2203,7 +2203,7 @@
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="2"/>
@@ -2215,7 +2215,7 @@
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="2"/>
@@ -2227,7 +2227,7 @@
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="2"/>
@@ -2239,7 +2239,7 @@
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="2"/>
@@ -2251,7 +2251,7 @@
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="2"/>
@@ -2263,7 +2263,7 @@
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="2"/>
@@ -2275,7 +2275,7 @@
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="2"/>
@@ -2287,7 +2287,7 @@
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="2"/>
@@ -2299,7 +2299,7 @@
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="2"/>
@@ -2311,7 +2311,7 @@
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="2"/>
@@ -2323,7 +2323,7 @@
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="2"/>
@@ -2335,7 +2335,7 @@
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="2"/>
@@ -2347,7 +2347,7 @@
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="2"/>
@@ -2359,7 +2359,7 @@
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="2"/>
@@ -2371,7 +2371,7 @@
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="2"/>
@@ -2383,7 +2383,7 @@
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="2"/>
@@ -2395,7 +2395,7 @@
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="2"/>
@@ -2407,7 +2407,7 @@
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="2"/>
@@ -2419,7 +2419,7 @@
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="2"/>
@@ -2431,7 +2431,7 @@
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="2"/>
@@ -2443,7 +2443,7 @@
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="2"/>
@@ -2455,7 +2455,7 @@
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="2"/>
@@ -2467,7 +2467,7 @@
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="2"/>
@@ -2479,7 +2479,7 @@
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="2"/>
@@ -2491,7 +2491,7 @@
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="2"/>
@@ -2503,7 +2503,7 @@
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="2"/>
@@ -2515,7 +2515,7 @@
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="2"/>
@@ -2527,7 +2527,7 @@
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="2"/>
@@ -2539,7 +2539,7 @@
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="2"/>
@@ -2551,7 +2551,7 @@
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="2"/>
@@ -2563,7 +2563,7 @@
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="2"/>
@@ -2575,7 +2575,7 @@
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="2"/>
@@ -2587,7 +2587,7 @@
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="2"/>
@@ -2599,7 +2599,7 @@
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="2"/>
@@ -2611,7 +2611,7 @@
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="2"/>
@@ -2623,7 +2623,7 @@
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="2"/>
@@ -2635,7 +2635,7 @@
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="2"/>
@@ -2647,7 +2647,7 @@
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="2"/>
@@ -2659,7 +2659,7 @@
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="2"/>
@@ -2671,7 +2671,7 @@
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="2"/>
@@ -2683,7 +2683,7 @@
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="2"/>
@@ -2695,7 +2695,7 @@
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="C153" s="2"/>
@@ -2707,7 +2707,7 @@
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="C154" s="2"/>
@@ -2719,7 +2719,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="C155" s="2"/>
@@ -2731,7 +2731,7 @@
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="2"/>
@@ -2743,7 +2743,7 @@
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="C157" s="2"/>
@@ -2755,7 +2755,7 @@
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="C158" s="2"/>
@@ -2767,7 +2767,7 @@
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="C159" s="2"/>
@@ -2779,7 +2779,7 @@
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="C160" s="2"/>
@@ -2791,7 +2791,7 @@
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="C161" s="2"/>
@@ -2803,7 +2803,7 @@
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="C162" s="2"/>
@@ -2815,7 +2815,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="C163" s="2"/>
@@ -2827,7 +2827,7 @@
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="C164" s="2"/>
@@ -2839,7 +2839,7 @@
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="C165" s="2"/>
@@ -2851,7 +2851,7 @@
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="C166" s="2"/>
@@ -2863,7 +2863,7 @@
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="2"/>
@@ -2875,7 +2875,7 @@
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="C168" s="2"/>
@@ -2887,7 +2887,7 @@
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="C169" s="2"/>
@@ -2899,7 +2899,7 @@
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="C170" s="2"/>
@@ -2911,7 +2911,7 @@
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="C171" s="2"/>
@@ -2923,7 +2923,7 @@
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="C172" s="2"/>
@@ -2935,7 +2935,7 @@
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="C173" s="2"/>
@@ -2947,7 +2947,7 @@
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="C174" s="2"/>
@@ -2959,7 +2959,7 @@
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="C175" s="2"/>
@@ -2971,7 +2971,7 @@
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="2"/>
@@ -2983,7 +2983,7 @@
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="C177" s="2"/>
@@ -2995,7 +2995,7 @@
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="C178" s="2"/>
@@ -3007,7 +3007,7 @@
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="C179" s="2"/>
@@ -3019,7 +3019,7 @@
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="C180" s="2"/>
@@ -3031,7 +3031,7 @@
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="C181" s="2"/>
@@ -3043,7 +3043,7 @@
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="C182" s="2"/>
@@ -3055,7 +3055,7 @@
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="C183" s="2"/>
@@ -3067,7 +3067,7 @@
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="C184" s="2"/>
@@ -3079,7 +3079,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="C185" s="2"/>
@@ -3091,7 +3091,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="2"/>
@@ -3103,7 +3103,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="C187" s="2"/>
@@ -3115,7 +3115,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="2"/>
@@ -3127,7 +3127,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="C189" s="2"/>
@@ -3139,7 +3139,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="C190" s="2"/>
@@ -3151,7 +3151,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="C191" s="2"/>
@@ -3163,7 +3163,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="C192" s="2"/>
@@ -3175,7 +3175,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="C193" s="2"/>
@@ -3187,7 +3187,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="C194" s="2"/>
@@ -3199,7 +3199,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="C195" s="2"/>
@@ -3211,7 +3211,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="2"/>
@@ -3223,7 +3223,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="2"/>
@@ -3235,7 +3235,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="3"/>
       <c r="C198" s="2"/>
@@ -3247,7 +3247,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="3"/>
       <c r="C199" s="2"/>
@@ -3259,7 +3259,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="3"/>
       <c r="C200" s="2"/>
@@ -3271,7 +3271,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="3"/>
       <c r="C201" s="2"/>
@@ -3283,7 +3283,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="3"/>
       <c r="C202" s="2"/>
@@ -3295,7 +3295,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" s="2"/>
       <c r="B203" s="3"/>
       <c r="C203" s="2"/>
@@ -3307,7 +3307,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" s="2"/>
       <c r="B204" s="3"/>
       <c r="C204" s="2"/>
@@ -3319,7 +3319,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205" s="2"/>
       <c r="B205" s="3"/>
       <c r="C205" s="2"/>
@@ -3331,7 +3331,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206" s="2"/>
       <c r="B206" s="3"/>
       <c r="C206" s="2"/>
@@ -3343,7 +3343,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207" s="2"/>
       <c r="B207" s="3"/>
       <c r="C207" s="2"/>
@@ -3355,7 +3355,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208" s="2"/>
       <c r="B208" s="3"/>
       <c r="C208" s="2"/>
@@ -3367,7 +3367,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209" s="2"/>
       <c r="B209" s="3"/>
       <c r="C209" s="2"/>
@@ -3379,7 +3379,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A210" s="2"/>
       <c r="B210" s="3"/>
       <c r="C210" s="2"/>
@@ -3391,7 +3391,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A211" s="2"/>
       <c r="B211" s="3"/>
       <c r="C211" s="2"/>
@@ -3403,7 +3403,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A212" s="2"/>
       <c r="B212" s="3"/>
       <c r="C212" s="2"/>
@@ -3415,7 +3415,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="3"/>
       <c r="C213" s="2"/>
@@ -3427,7 +3427,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A214" s="2"/>
       <c r="B214" s="3"/>
       <c r="C214" s="2"/>
@@ -3439,7 +3439,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A215" s="2"/>
       <c r="B215" s="3"/>
       <c r="C215" s="2"/>
@@ -3451,7 +3451,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A216" s="2"/>
       <c r="B216" s="3"/>
       <c r="C216" s="2"/>
@@ -3463,7 +3463,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A217" s="2"/>
       <c r="B217" s="3"/>
       <c r="C217" s="2"/>
@@ -3475,7 +3475,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A218" s="2"/>
       <c r="B218" s="3"/>
       <c r="C218" s="2"/>
@@ -3487,7 +3487,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A219" s="2"/>
       <c r="B219" s="3"/>
       <c r="C219" s="2"/>
@@ -3499,7 +3499,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A220" s="2"/>
       <c r="B220" s="3"/>
       <c r="C220" s="2"/>
@@ -3511,7 +3511,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A221" s="2"/>
       <c r="B221" s="3"/>
       <c r="C221" s="2"/>
@@ -3523,7 +3523,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A222" s="2"/>
       <c r="B222" s="3"/>
       <c r="C222" s="2"/>
@@ -3535,7 +3535,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A223" s="2"/>
       <c r="B223" s="3"/>
       <c r="C223" s="2"/>
@@ -3547,7 +3547,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A224" s="2"/>
       <c r="B224" s="3"/>
       <c r="C224" s="2"/>
@@ -3559,7 +3559,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A225" s="2"/>
       <c r="B225" s="3"/>
       <c r="C225" s="2"/>
@@ -3571,7 +3571,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A226" s="2"/>
       <c r="B226" s="3"/>
       <c r="C226" s="2"/>
@@ -3583,7 +3583,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A227" s="2"/>
       <c r="B227" s="3"/>
       <c r="C227" s="2"/>
@@ -3595,7 +3595,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="3"/>
       <c r="C228" s="2"/>
@@ -3607,7 +3607,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
       <c r="B229" s="3"/>
       <c r="C229" s="2"/>
@@ -3619,7 +3619,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A230" s="2"/>
       <c r="B230" s="3"/>
       <c r="C230" s="2"/>
@@ -3631,7 +3631,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A231" s="2"/>
       <c r="B231" s="3"/>
       <c r="C231" s="2"/>
@@ -3643,7 +3643,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A232" s="2"/>
       <c r="B232" s="3"/>
       <c r="C232" s="2"/>
@@ -3655,7 +3655,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A233" s="2"/>
       <c r="B233" s="3"/>
       <c r="C233" s="2"/>
@@ -3667,7 +3667,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A234" s="2"/>
       <c r="B234" s="3"/>
       <c r="C234" s="2"/>
@@ -3679,7 +3679,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A235" s="2"/>
       <c r="B235" s="3"/>
       <c r="C235" s="2"/>
@@ -3691,7 +3691,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A236" s="2"/>
       <c r="B236" s="3"/>
       <c r="C236" s="2"/>
@@ -3703,7 +3703,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A237" s="2"/>
       <c r="B237" s="3"/>
       <c r="C237" s="2"/>
@@ -3715,7 +3715,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A238" s="2"/>
       <c r="B238" s="3"/>
       <c r="C238" s="2"/>
@@ -3727,7 +3727,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A239" s="2"/>
       <c r="B239" s="3"/>
       <c r="C239" s="2"/>
@@ -3739,7 +3739,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A240" s="2"/>
       <c r="B240" s="3"/>
       <c r="C240" s="2"/>
@@ -3751,7 +3751,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A241" s="2"/>
       <c r="B241" s="3"/>
       <c r="C241" s="2"/>
@@ -3763,7 +3763,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A242" s="2"/>
       <c r="B242" s="3"/>
       <c r="C242" s="2"/>
@@ -3775,7 +3775,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="3"/>
       <c r="C243" s="2"/>
@@ -3787,7 +3787,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A244" s="2"/>
       <c r="B244" s="3"/>
       <c r="C244" s="2"/>
@@ -3799,7 +3799,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A245" s="2"/>
       <c r="B245" s="3"/>
       <c r="C245" s="2"/>
@@ -3811,7 +3811,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A246" s="2"/>
       <c r="B246" s="3"/>
       <c r="C246" s="2"/>
@@ -3823,7 +3823,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A247" s="2"/>
       <c r="B247" s="3"/>
       <c r="C247" s="2"/>
@@ -3835,7 +3835,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A248" s="2"/>
       <c r="B248" s="3"/>
       <c r="C248" s="2"/>
@@ -3847,7 +3847,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A249" s="2"/>
       <c r="B249" s="3"/>
       <c r="C249" s="2"/>
@@ -3859,7 +3859,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A250" s="2"/>
       <c r="B250" s="3"/>
       <c r="C250" s="2"/>
@@ -3871,7 +3871,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A251" s="2"/>
       <c r="B251" s="3"/>
       <c r="C251" s="2"/>
@@ -3883,7 +3883,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A252" s="2"/>
       <c r="B252" s="3"/>
       <c r="C252" s="2"/>
@@ -3895,7 +3895,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A253" s="2"/>
       <c r="B253" s="3"/>
       <c r="C253" s="2"/>
@@ -3907,7 +3907,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A254" s="2"/>
       <c r="B254" s="3"/>
       <c r="C254" s="2"/>
@@ -3919,7 +3919,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A255" s="2"/>
       <c r="B255" s="3"/>
       <c r="C255" s="2"/>
@@ -3931,7 +3931,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A256" s="2"/>
       <c r="B256" s="3"/>
       <c r="C256" s="2"/>
@@ -3943,7 +3943,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A257" s="2"/>
       <c r="B257" s="3"/>
       <c r="C257" s="2"/>
@@ -3955,7 +3955,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A258" s="2"/>
       <c r="B258" s="3"/>
       <c r="C258" s="2"/>
@@ -3967,7 +3967,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A259" s="2"/>
       <c r="B259" s="3"/>
       <c r="C259" s="2"/>
@@ -3979,7 +3979,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A260" s="2"/>
       <c r="B260" s="3"/>
       <c r="C260" s="2"/>
@@ -3991,7 +3991,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A261" s="2"/>
       <c r="B261" s="3"/>
       <c r="C261" s="2"/>
@@ -4003,7 +4003,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A262" s="2"/>
       <c r="B262" s="3"/>
       <c r="C262" s="2"/>
@@ -4015,7 +4015,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A263" s="2"/>
       <c r="B263" s="3"/>
       <c r="C263" s="2"/>
@@ -4027,7 +4027,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A264" s="2"/>
       <c r="B264" s="3"/>
       <c r="C264" s="2"/>
@@ -4039,7 +4039,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A265" s="2"/>
       <c r="B265" s="3"/>
       <c r="C265" s="2"/>
@@ -4051,7 +4051,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A266" s="2"/>
       <c r="B266" s="3"/>
       <c r="C266" s="2"/>
@@ -4063,7 +4063,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A267" s="2"/>
       <c r="B267" s="3"/>
       <c r="C267" s="2"/>
@@ -4075,7 +4075,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A268" s="2"/>
       <c r="B268" s="3"/>
       <c r="C268" s="2"/>
@@ -4087,7 +4087,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A269" s="2"/>
       <c r="B269" s="3"/>
       <c r="C269" s="2"/>
@@ -4099,7 +4099,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A270" s="2"/>
       <c r="B270" s="3"/>
       <c r="C270" s="2"/>
@@ -4111,7 +4111,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A271" s="2"/>
       <c r="B271" s="3"/>
       <c r="C271" s="2"/>
@@ -4123,7 +4123,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A272" s="2"/>
       <c r="B272" s="3"/>
       <c r="C272" s="2"/>
@@ -4135,7 +4135,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A273" s="2"/>
       <c r="B273" s="3"/>
       <c r="C273" s="2"/>
@@ -4147,7 +4147,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A274" s="2"/>
       <c r="B274" s="3"/>
       <c r="C274" s="2"/>
@@ -4159,7 +4159,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A275" s="2"/>
       <c r="B275" s="3"/>
       <c r="C275" s="2"/>
@@ -4171,7 +4171,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A276" s="2"/>
       <c r="B276" s="3"/>
       <c r="C276" s="2"/>
@@ -4183,7 +4183,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A277" s="2"/>
       <c r="B277" s="3"/>
       <c r="C277" s="2"/>
@@ -4195,7 +4195,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A278" s="2"/>
       <c r="B278" s="3"/>
       <c r="C278" s="2"/>
@@ -4207,7 +4207,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A279" s="2"/>
       <c r="B279" s="3"/>
       <c r="C279" s="2"/>
@@ -4219,7 +4219,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A280" s="2"/>
       <c r="B280" s="3"/>
       <c r="C280" s="2"/>
@@ -4231,7 +4231,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A281" s="2"/>
       <c r="B281" s="3"/>
       <c r="C281" s="2"/>
@@ -4243,7 +4243,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A282" s="2"/>
       <c r="B282" s="3"/>
       <c r="C282" s="2"/>
@@ -4255,7 +4255,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A283" s="2"/>
       <c r="B283" s="3"/>
       <c r="C283" s="2"/>
@@ -4267,7 +4267,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A284" s="2"/>
       <c r="B284" s="3"/>
       <c r="C284" s="2"/>
@@ -4279,7 +4279,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A285" s="2"/>
       <c r="B285" s="3"/>
       <c r="C285" s="2"/>
@@ -4291,7 +4291,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A286" s="2"/>
       <c r="B286" s="3"/>
       <c r="C286" s="2"/>
@@ -4303,7 +4303,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A287" s="2"/>
       <c r="B287" s="3"/>
       <c r="C287" s="2"/>
@@ -4315,7 +4315,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A288" s="2"/>
       <c r="B288" s="3"/>
       <c r="C288" s="2"/>
@@ -4327,7 +4327,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A289" s="2"/>
       <c r="B289" s="3"/>
       <c r="C289" s="2"/>
@@ -4339,7 +4339,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A290" s="2"/>
       <c r="B290" s="3"/>
       <c r="C290" s="2"/>
@@ -4351,7 +4351,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A291" s="2"/>
       <c r="B291" s="3"/>
       <c r="C291" s="2"/>
@@ -4363,7 +4363,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A292" s="2"/>
       <c r="B292" s="3"/>
       <c r="C292" s="2"/>
@@ -4375,7 +4375,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A293" s="2"/>
       <c r="B293" s="3"/>
       <c r="C293" s="2"/>
@@ -4387,7 +4387,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A294" s="2"/>
       <c r="B294" s="3"/>
       <c r="C294" s="2"/>
@@ -4399,7 +4399,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A295" s="2"/>
       <c r="B295" s="3"/>
       <c r="C295" s="2"/>
@@ -4411,7 +4411,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A296" s="2"/>
       <c r="B296" s="3"/>
       <c r="C296" s="2"/>
@@ -4423,7 +4423,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A297" s="2"/>
       <c r="B297" s="3"/>
       <c r="C297" s="2"/>
@@ -4435,7 +4435,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A298" s="2"/>
       <c r="B298" s="3"/>
       <c r="C298" s="2"/>
@@ -4447,7 +4447,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A299" s="2"/>
       <c r="B299" s="3"/>
       <c r="C299" s="2"/>
@@ -4459,7 +4459,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A300" s="2"/>
       <c r="B300" s="3"/>
       <c r="C300" s="2"/>
@@ -4471,7 +4471,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A301" s="2"/>
       <c r="B301" s="3"/>
       <c r="C301" s="2"/>
@@ -4483,7 +4483,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A302" s="2"/>
       <c r="B302" s="3"/>
       <c r="C302" s="2"/>
@@ -4495,7 +4495,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A303" s="2"/>
       <c r="B303" s="3"/>
       <c r="C303" s="2"/>
@@ -4507,7 +4507,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A304" s="2"/>
       <c r="B304" s="3"/>
       <c r="C304" s="2"/>
@@ -4519,7 +4519,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A305" s="2"/>
       <c r="B305" s="3"/>
       <c r="C305" s="2"/>
@@ -4531,7 +4531,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A306" s="2"/>
       <c r="B306" s="3"/>
       <c r="C306" s="2"/>
@@ -4543,7 +4543,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A307" s="2"/>
       <c r="B307" s="3"/>
       <c r="C307" s="2"/>
@@ -4555,7 +4555,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A308" s="2"/>
       <c r="B308" s="3"/>
       <c r="C308" s="2"/>
@@ -4567,7 +4567,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A309" s="2"/>
       <c r="B309" s="3"/>
       <c r="C309" s="2"/>
@@ -4579,7 +4579,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A310" s="2"/>
       <c r="B310" s="3"/>
       <c r="C310" s="2"/>
@@ -4591,7 +4591,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A311" s="2"/>
       <c r="B311" s="3"/>
       <c r="C311" s="2"/>
@@ -4603,7 +4603,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A312" s="2"/>
       <c r="B312" s="3"/>
       <c r="C312" s="2"/>
@@ -4615,7 +4615,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A313" s="2"/>
       <c r="B313" s="3"/>
       <c r="C313" s="2"/>
@@ -4627,7 +4627,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A314" s="2"/>
       <c r="B314" s="3"/>
       <c r="C314" s="2"/>
@@ -4639,7 +4639,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A315" s="2"/>
       <c r="B315" s="3"/>
       <c r="C315" s="2"/>
@@ -4651,7 +4651,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A316" s="2"/>
       <c r="B316" s="3"/>
       <c r="C316" s="2"/>
@@ -4663,7 +4663,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A317" s="2"/>
       <c r="B317" s="3"/>
       <c r="C317" s="2"/>
@@ -4675,7 +4675,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A318" s="2"/>
       <c r="B318" s="3"/>
       <c r="C318" s="2"/>
@@ -4687,7 +4687,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A319" s="2"/>
       <c r="B319" s="3"/>
       <c r="C319" s="2"/>
@@ -4699,7 +4699,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A320" s="2"/>
       <c r="B320" s="3"/>
       <c r="C320" s="2"/>
@@ -4711,7 +4711,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A321" s="2"/>
       <c r="B321" s="3"/>
       <c r="C321" s="2"/>
@@ -4723,7 +4723,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A322" s="2"/>
       <c r="B322" s="3"/>
       <c r="C322" s="2"/>
@@ -4735,7 +4735,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A323" s="2"/>
       <c r="B323" s="3"/>
       <c r="C323" s="2"/>
@@ -4747,7 +4747,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A324" s="2"/>
       <c r="B324" s="3"/>
       <c r="C324" s="2"/>
@@ -4759,7 +4759,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A325" s="2"/>
       <c r="B325" s="3"/>
       <c r="C325" s="2"/>
@@ -4771,7 +4771,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A326" s="2"/>
       <c r="B326" s="3"/>
       <c r="C326" s="2"/>
@@ -4783,7 +4783,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A327" s="2"/>
       <c r="B327" s="3"/>
       <c r="C327" s="2"/>
@@ -4795,7 +4795,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A328" s="2"/>
       <c r="B328" s="3"/>
       <c r="C328" s="2"/>
@@ -4807,7 +4807,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A329" s="2"/>
       <c r="B329" s="3"/>
       <c r="C329" s="2"/>
@@ -4819,7 +4819,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A330" s="2"/>
       <c r="B330" s="3"/>
       <c r="C330" s="2"/>
@@ -4831,7 +4831,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A331" s="2"/>
       <c r="B331" s="3"/>
       <c r="C331" s="2"/>
@@ -4843,7 +4843,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A332" s="2"/>
       <c r="B332" s="3"/>
       <c r="C332" s="2"/>
@@ -4855,7 +4855,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A333" s="2"/>
       <c r="B333" s="3"/>
       <c r="C333" s="2"/>
@@ -4867,7 +4867,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A334" s="2"/>
       <c r="B334" s="3"/>
       <c r="C334" s="2"/>
@@ -4879,7 +4879,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A335" s="2"/>
       <c r="B335" s="3"/>
       <c r="C335" s="2"/>
@@ -4891,7 +4891,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A336" s="2"/>
       <c r="B336" s="3"/>
       <c r="C336" s="2"/>
@@ -4903,7 +4903,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A337" s="2"/>
       <c r="B337" s="3"/>
       <c r="C337" s="2"/>
@@ -4915,7 +4915,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A338" s="2"/>
       <c r="B338" s="3"/>
       <c r="C338" s="2"/>
@@ -4927,7 +4927,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A339" s="2"/>
       <c r="B339" s="3"/>
       <c r="C339" s="2"/>
@@ -4939,7 +4939,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A340" s="2"/>
       <c r="B340" s="3"/>
       <c r="C340" s="2"/>
@@ -4951,7 +4951,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A341" s="2"/>
       <c r="B341" s="3"/>
       <c r="C341" s="2"/>
@@ -4963,7 +4963,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A342" s="2"/>
       <c r="B342" s="3"/>
       <c r="C342" s="2"/>
@@ -4975,7 +4975,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A343" s="2"/>
       <c r="B343" s="3"/>
       <c r="C343" s="2"/>
@@ -4987,7 +4987,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A344" s="2"/>
       <c r="B344" s="3"/>
       <c r="C344" s="2"/>
@@ -4999,7 +4999,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A345" s="2"/>
       <c r="B345" s="3"/>
       <c r="C345" s="2"/>
@@ -5011,7 +5011,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A346" s="2"/>
       <c r="B346" s="3"/>
       <c r="C346" s="2"/>
@@ -5023,7 +5023,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A347" s="2"/>
       <c r="B347" s="3"/>
       <c r="C347" s="2"/>
@@ -5035,7 +5035,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A348" s="2"/>
       <c r="B348" s="3"/>
       <c r="C348" s="2"/>
@@ -5047,7 +5047,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A349" s="2"/>
       <c r="B349" s="3"/>
       <c r="C349" s="2"/>
@@ -5059,7 +5059,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A350" s="2"/>
       <c r="B350" s="3"/>
       <c r="C350" s="2"/>
@@ -5071,7 +5071,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A351" s="2"/>
       <c r="B351" s="3"/>
       <c r="C351" s="2"/>
@@ -5083,7 +5083,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A352" s="2"/>
       <c r="B352" s="3"/>
       <c r="C352" s="2"/>
@@ -5095,7 +5095,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A353" s="2"/>
       <c r="B353" s="3"/>
       <c r="C353" s="2"/>
@@ -5107,7 +5107,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A354" s="2"/>
       <c r="B354" s="3"/>
       <c r="C354" s="2"/>
@@ -5119,7 +5119,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A355" s="2"/>
       <c r="B355" s="3"/>
       <c r="C355" s="2"/>
@@ -5131,7 +5131,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A356" s="2"/>
       <c r="B356" s="3"/>
       <c r="C356" s="2"/>
@@ -5143,7 +5143,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A357" s="2"/>
       <c r="B357" s="3"/>
       <c r="C357" s="2"/>
@@ -5155,7 +5155,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A358" s="2"/>
       <c r="B358" s="3"/>
       <c r="C358" s="2"/>
@@ -5167,7 +5167,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A359" s="2"/>
       <c r="B359" s="3"/>
       <c r="C359" s="2"/>
@@ -5179,7 +5179,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A360" s="2"/>
       <c r="B360" s="3"/>
       <c r="C360" s="2"/>
@@ -5191,7 +5191,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A361" s="2"/>
       <c r="B361" s="3"/>
       <c r="C361" s="2"/>
@@ -5203,7 +5203,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A362" s="2"/>
       <c r="B362" s="3"/>
       <c r="C362" s="2"/>
@@ -5215,7 +5215,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A363" s="2"/>
       <c r="B363" s="3"/>
       <c r="C363" s="2"/>
@@ -5227,7 +5227,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A364" s="2"/>
       <c r="B364" s="3"/>
       <c r="C364" s="2"/>
@@ -5239,7 +5239,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A365" s="2"/>
       <c r="B365" s="3"/>
       <c r="C365" s="2"/>
@@ -5251,7 +5251,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A366" s="2"/>
       <c r="B366" s="3"/>
       <c r="C366" s="2"/>
@@ -5263,7 +5263,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A367" s="2"/>
       <c r="B367" s="3"/>
       <c r="C367" s="2"/>
@@ -5275,7 +5275,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A368" s="2"/>
       <c r="B368" s="3"/>
       <c r="C368" s="2"/>
@@ -5287,7 +5287,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A369" s="2"/>
       <c r="B369" s="3"/>
       <c r="C369" s="2"/>
@@ -5299,7 +5299,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A370" s="2"/>
       <c r="B370" s="3"/>
       <c r="C370" s="2"/>
@@ -5311,7 +5311,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A371" s="2"/>
       <c r="B371" s="3"/>
       <c r="C371" s="2"/>
@@ -5323,7 +5323,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A372" s="2"/>
       <c r="B372" s="3"/>
       <c r="C372" s="2"/>
@@ -5335,7 +5335,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A373" s="2"/>
       <c r="B373" s="3"/>
       <c r="C373" s="2"/>
@@ -5347,7 +5347,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A374" s="2"/>
       <c r="B374" s="3"/>
       <c r="C374" s="2"/>
@@ -5359,7 +5359,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A375" s="2"/>
       <c r="B375" s="3"/>
       <c r="C375" s="2"/>
@@ -5371,7 +5371,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A376" s="2"/>
       <c r="B376" s="3"/>
       <c r="C376" s="2"/>
@@ -5383,7 +5383,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A377" s="2"/>
       <c r="B377" s="3"/>
       <c r="C377" s="2"/>
@@ -5395,7 +5395,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A378" s="2"/>
       <c r="B378" s="3"/>
       <c r="C378" s="2"/>
@@ -5407,7 +5407,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A379" s="2"/>
       <c r="B379" s="3"/>
       <c r="C379" s="2"/>
@@ -5419,7 +5419,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A380" s="2"/>
       <c r="B380" s="3"/>
       <c r="C380" s="2"/>
@@ -5431,7 +5431,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A381" s="2"/>
       <c r="B381" s="3"/>
       <c r="C381" s="2"/>
@@ -5443,7 +5443,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A382" s="2"/>
       <c r="B382" s="3"/>
       <c r="C382" s="2"/>
@@ -5455,7 +5455,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A383" s="2"/>
       <c r="B383" s="3"/>
       <c r="C383" s="2"/>
@@ -5467,7 +5467,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A384" s="2"/>
       <c r="B384" s="3"/>
       <c r="C384" s="2"/>
@@ -5479,7 +5479,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A385" s="2"/>
       <c r="B385" s="3"/>
       <c r="C385" s="2"/>
@@ -5491,7 +5491,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A386" s="2"/>
       <c r="B386" s="3"/>
       <c r="C386" s="2"/>
@@ -5503,7 +5503,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A387" s="2"/>
       <c r="B387" s="3"/>
       <c r="C387" s="2"/>
@@ -5515,7 +5515,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A388" s="2"/>
       <c r="B388" s="3"/>
       <c r="C388" s="2"/>
@@ -5527,7 +5527,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A389" s="2"/>
       <c r="B389" s="3"/>
       <c r="C389" s="2"/>
@@ -5539,7 +5539,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A390" s="2"/>
       <c r="B390" s="3"/>
       <c r="C390" s="2"/>
@@ -5551,7 +5551,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A391" s="2"/>
       <c r="B391" s="3"/>
       <c r="C391" s="2"/>
@@ -5563,7 +5563,7 @@
       <c r="I391" s="3"/>
       <c r="J391" s="3"/>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A392" s="2"/>
       <c r="B392" s="3"/>
       <c r="C392" s="2"/>
@@ -5575,7 +5575,7 @@
       <c r="I392" s="3"/>
       <c r="J392" s="3"/>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A393" s="2"/>
       <c r="B393" s="3"/>
       <c r="C393" s="2"/>
@@ -5587,7 +5587,7 @@
       <c r="I393" s="3"/>
       <c r="J393" s="3"/>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A394" s="2"/>
       <c r="B394" s="3"/>
       <c r="C394" s="2"/>
@@ -5599,7 +5599,7 @@
       <c r="I394" s="3"/>
       <c r="J394" s="3"/>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A395" s="2"/>
       <c r="B395" s="3"/>
       <c r="C395" s="2"/>
@@ -5611,7 +5611,7 @@
       <c r="I395" s="3"/>
       <c r="J395" s="3"/>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A396" s="2"/>
       <c r="B396" s="3"/>
       <c r="C396" s="2"/>
@@ -5623,7 +5623,7 @@
       <c r="I396" s="3"/>
       <c r="J396" s="3"/>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A397" s="2"/>
       <c r="B397" s="3"/>
       <c r="C397" s="2"/>
@@ -5635,7 +5635,7 @@
       <c r="I397" s="3"/>
       <c r="J397" s="3"/>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A398" s="2"/>
       <c r="B398" s="3"/>
       <c r="C398" s="2"/>
@@ -5647,7 +5647,7 @@
       <c r="I398" s="3"/>
       <c r="J398" s="3"/>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A399" s="2"/>
       <c r="B399" s="3"/>
       <c r="C399" s="2"/>
@@ -5659,7 +5659,7 @@
       <c r="I399" s="3"/>
       <c r="J399" s="3"/>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A400" s="2"/>
       <c r="B400" s="3"/>
       <c r="C400" s="2"/>
@@ -5671,21 +5671,8 @@
       <c r="I400" s="3"/>
       <c r="J400" s="3"/>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A401" s="2"/>
-      <c r="B401" s="3"/>
-      <c r="C401" s="2"/>
-      <c r="D401" s="3"/>
-      <c r="E401" s="3"/>
-      <c r="F401" s="3"/>
-      <c r="G401" s="2"/>
-      <c r="H401" s="2"/>
-      <c r="I401" s="3"/>
-      <c r="J401" s="3"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K008000 OFFICIAL&amp;1#_x000D_</oddHeader>
@@ -5698,13 +5685,13 @@
           <x14:formula1>
             <xm:f>רשימות!$A$1:$A$15</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D6 B2:B401</xm:sqref>
+          <xm:sqref>B7:B400</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>רשימות!$B$1:$B$10</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E401</xm:sqref>
+          <xm:sqref>E7:E400</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5715,7 +5702,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E200"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -5724,7 +5711,7 @@
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5741,7 +5728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -5749,1395 +5736,1395 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1573</v>
+        <v>18</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -7181,482 +7168,484 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A149"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
     </row>
   </sheetData>
@@ -7672,210 +7661,210 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="19"/>
     </row>
-    <row r="4" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B4" s="19"/>
     </row>
-    <row r="5" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" s="19"/>
     </row>
-    <row r="6" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="19"/>
     </row>
-    <row r="7" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" s="19"/>
     </row>
-    <row r="8" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="19"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
       <c r="B13" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11"/>
       <c r="B14" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14"/>
       <c r="B17" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="16"/>
       <c r="B19" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
         <v>11</v>
       </c>
       <c r="B23" s="19"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="19"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B25" s="19"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B26" s="19"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B27" s="19"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B28" s="19"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B29" s="19"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B30" s="19"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B31" s="19"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B32" s="19"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B33" s="19"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B34" s="19"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B35" s="19"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B36" s="19"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B37" s="19"/>
     </row>
@@ -7914,12 +7903,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -7927,131 +7916,131 @@
         <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/itinerary.xlsx
+++ b/public/data/itinerary.xlsx
@@ -5711,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="19" min="1" max="1"/>
@@ -5753,20 +5753,25 @@
       </c>
       <c r="F1" s="21" t="inlineStr">
         <is>
+          <t>קישור לאישור הזמנה / מסמך</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
           <t>מחיר</t>
         </is>
       </c>
-      <c r="G1" s="21" t="inlineStr">
+      <c r="H1" s="21" t="inlineStr">
         <is>
           <t>מטבע</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
+      <c r="I1" s="21" t="inlineStr">
         <is>
           <t>שולם? (כן/לא)</t>
         </is>
       </c>
-      <c r="I1" s="21" t="inlineStr">
+      <c r="J1" s="21" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
@@ -5794,22 +5799,23 @@
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr"/>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr"/>
+      <c r="G2" s="22" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
       </c>
-      <c r="G2" s="22" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="H2" s="22" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>דוגמה בלבד — מחקו שורה זו</t>
         </is>
@@ -5817,10 +5823,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>CurrencyList</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>PaidList</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/data/itinerary.xlsx
+++ b/public/data/itinerary.xlsx
@@ -9,10 +9,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לוז" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="טיסות" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מלונות" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תקציב" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אריזה" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקרא והוראות" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="רשימות" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מסעדות" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אטרקציות" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תקציב" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="אריזה" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקרא והוראות" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="רשימות" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="PlacesList">רשימות!$A$1:$A$15</definedName>
@@ -20,9 +22,10 @@
     <definedName name="BudgetCats">רשימות!$C$1:$C$7</definedName>
     <definedName name="CurrencyList">רשימות!$D$1:$D$3</definedName>
     <definedName name="PaidList">רשימות!$E$1:$E$2</definedName>
+    <definedName name="RestCats">רשימות!$F$1:$F$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'לוז'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'תקציב'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'אריזה'!$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'תקציב'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'אריזה'!$A$1</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -5608,7 +5611,7 @@
     <row r="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>תאריך (YYYY-MM-DD)</t>
+          <t>תאריך</t>
         </is>
       </c>
       <c r="B1" s="21" t="inlineStr">
@@ -5655,7 +5658,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>5.9.2026</t>
         </is>
       </c>
       <c r="B2" s="22" t="inlineStr">
@@ -5738,12 +5741,12 @@
       </c>
       <c r="C1" s="21" t="inlineStr">
         <is>
-          <t>תאריך צ׳ק-אין (YYYY-MM-DD)</t>
+          <t>תאריכי שהייה</t>
         </is>
       </c>
       <c r="D1" s="21" t="inlineStr">
         <is>
-          <t>מספר לילות</t>
+          <t>מספר לילות (רשות)</t>
         </is>
       </c>
       <c r="E1" s="21" t="inlineStr">
@@ -5790,14 +5793,10 @@
       </c>
       <c r="C2" s="22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="D2" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>6.9.2026-10.9.2026</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr"/>
       <c r="E2" s="22" t="inlineStr"/>
       <c r="F2" s="22" t="inlineStr"/>
       <c r="G2" s="22" t="inlineStr">
@@ -5835,6 +5834,200 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="19" min="1" max="1"/>
+    <col width="14" customWidth="1" style="19" min="2" max="2"/>
+    <col width="14" customWidth="1" style="19" min="3" max="3"/>
+    <col width="14" customWidth="1" style="19" min="4" max="4"/>
+    <col width="10" customWidth="1" style="19" min="5" max="5"/>
+    <col width="30" customWidth="1" style="19" min="6" max="6"/>
+    <col width="30" customWidth="1" style="19" min="7" max="7"/>
+    <col width="30" customWidth="1" style="19" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>שם</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>קטגוריה</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>עיר</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>שעה</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>קישור לאישור הזמנה</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>קישור Google Maps</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>הערות</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>מסעדת דוגמה</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>מסעדה</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>טוקיו</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>6.9.2026</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F2" s="22" t="inlineStr"/>
+      <c r="G2" s="22" t="inlineStr"/>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>דוגמה בלבד — מחקו שורה זו</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>RestCats</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" style="19" min="1" max="1"/>
+    <col width="14" customWidth="1" style="19" min="2" max="2"/>
+    <col width="14" customWidth="1" style="19" min="3" max="3"/>
+    <col width="10" customWidth="1" style="19" min="4" max="4"/>
+    <col width="30" customWidth="1" style="19" min="5" max="5"/>
+    <col width="30" customWidth="1" style="19" min="6" max="6"/>
+    <col width="30" customWidth="1" style="19" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>שם</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>עיר</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>שעה</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>קישור לכרטיסים</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>קישור Google Maps</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>הערות</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>אטרקציית דוגמה</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>אוסקה</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>7.9.2026</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr"/>
+      <c r="F2" s="22" t="inlineStr"/>
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>דוגמה בלבד — מחקו שורה זו</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7315,7 +7508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7844,7 +8037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8141,13 +8334,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="22" customWidth="1" style="19" min="1" max="4"/>
@@ -8179,6 +8372,11 @@
           <t>כן</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>מסעדה</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8206,6 +8404,11 @@
           <t>לא</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>בית קפה</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8228,6 +8431,11 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>בר</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8245,6 +8453,11 @@
           <t>אטרקציות וכרטיסים</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>מועדון</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8262,6 +8475,11 @@
           <t>קניות</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>בייקרי</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8279,6 +8497,11 @@
           <t>תחבורה מקומית</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>איזקאיה</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8296,6 +8519,11 @@
           <t>אחר</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>שוק</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8306,6 +8534,11 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>טיסה</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>קינוח</t>
         </is>
       </c>
     </row>
